--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
@@ -1,22 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\BERNARDO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BB97B6-694A-4182-BCF9-52ACEE2E9B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Facturas" sheetId="1" r:id="rId4"/>
-    <sheet name="Fichas" sheetId="2" r:id="rId5"/>
+    <sheet name="Facturas" sheetId="1" r:id="rId1"/>
+    <sheet name="Fichas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="68">
   <si>
     <t>Facturas De Bernardo</t>
   </si>
@@ -39,10 +57,172 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>05EB63DC-7FA9-41C1-A059-C7252051557A</t>
+  </si>
+  <si>
+    <t>02/05/2026</t>
+  </si>
+  <si>
     <t>INGRESO</t>
   </si>
   <si>
+    <t>099EF06B-66E8-4475-8EDE-84C6E7FDA663</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>0BA77652-9394-49C3-97C5-97DC26317082</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>0E4022D0-BCE2-4973-BDDA-1FCA18FB834E</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>1CD2BDA8-B267-48ED-8F38-3A3F8139E924</t>
+  </si>
+  <si>
+    <t>20A8160B-7B52-4F0F-B046-CF1E955270B4</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>25E8545E-DD77-5213-9E83-1EA56CE690DA</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>2FAFB2B7-0EB4-4DD2-A41E-3FDFB136DE22</t>
+  </si>
+  <si>
+    <t>36B58A3F-D6F6-4334-9122-87D4C719E277</t>
+  </si>
+  <si>
+    <t>38E0D21E-8074-424F-B222-9907EA5A3A67</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>417FAB87-B895-42E1-ADC6-B26E156E4B49</t>
+  </si>
+  <si>
+    <t>458BE5F3-2C1B-4F07-83CD-30A9A184B3E2</t>
+  </si>
+  <si>
+    <t>4A9394D8-A510-509E-9D98-E1C8CF71A7A4</t>
+  </si>
+  <si>
+    <t>4D2D1FD6-1485-5F0D-ABAA-45F5F2953C93</t>
+  </si>
+  <si>
+    <t>5B400010-AC82-4B8F-BF94-0E39B70C0B56</t>
+  </si>
+  <si>
+    <t>60331495-8504-4E37-85B6-999EC3A7D83D</t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>6C7748B8-624B-5F70-A73A-2AD2A6CF2F95</t>
+  </si>
+  <si>
+    <t>6D246322-A879-4456-99EA-9D374101EF7B</t>
+  </si>
+  <si>
+    <t>7799DA6D-EB21-55CB-AC82-24FDA948522F</t>
+  </si>
+  <si>
+    <t>7F23180A-4B6D-406C-8CFE-97DC2631992A</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>8891BA1B-0528-43F6-A2C0-AB69258810A2</t>
+  </si>
+  <si>
+    <t>9D56EE85-48C6-4A6C-803A-49003CFC3452</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
     <t>PAGO</t>
+  </si>
+  <si>
+    <t>DFDCC6FE-9AD3-4B6B-823C-589A31FF34EB</t>
+  </si>
+  <si>
+    <t>01/05/2026</t>
+  </si>
+  <si>
+    <t>A3674DA6-DED2-41D2-963C-A59C62B8C04C</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>A97953A2-3053-4E2B-9560-5E02E5E675BD</t>
+  </si>
+  <si>
+    <t>ACC74A02-CADC-5DA3-BB5B-6AA8F8F0443D</t>
+  </si>
+  <si>
+    <t>ADBDE4BD-1C2E-401C-A876-BEFEFD8B5041</t>
+  </si>
+  <si>
+    <t>AEB92FC3-26C8-4EEB-8AA8-39BA97877B01</t>
+  </si>
+  <si>
+    <t>09/05/2026</t>
+  </si>
+  <si>
+    <t>B7037D06-DEAF-47BB-A013-ACD1E4CBE5F7</t>
+  </si>
+  <si>
+    <t>BE607ADE-E1C4-465F-BC3D-B12D4109BE92</t>
+  </si>
+  <si>
+    <t>CFC606C3-15C7-4C12-A1E6-C07B424B8E52</t>
+  </si>
+  <si>
+    <t>31/05/2026</t>
+  </si>
+  <si>
+    <t>D2D97534-FD69-4212-96CE-6725D6EA60C0</t>
+  </si>
+  <si>
+    <t>D7D50518-5B54-57EA-A659-D25D514557A7</t>
+  </si>
+  <si>
+    <t>DF81EAB6-C9CC-497D-954A-4066EF87754B</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>E3D349FA-9FFA-4C37-9034-19504D984E65</t>
+  </si>
+  <si>
+    <t>E4075E7A-623E-4DE0-8999-79124B1C70A4</t>
+  </si>
+  <si>
+    <t>E8EB5B99-7A21-4AE0-A9E1-E820DE7DD3DB</t>
+  </si>
+  <si>
+    <t>F2A339F5-59A8-4C97-A664-23F5E1389E94</t>
+  </si>
+  <si>
+    <t>F2EA580E-5B8F-45D4-B98C-FBD498F55106</t>
   </si>
   <si>
     <t>Total</t>
@@ -63,52 +243,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF548235"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -173,33 +337,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -489,31 +661,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -530,516 +699,672 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="5"/>
+      <c r="B5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D5" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="7">
         <v>12126.34</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="8"/>
+      <c r="B6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="D6" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10">
         <v>572.64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D7" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
+      <c r="B8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="D8" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="10">
-        <v>200000.0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D9" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" s="7">
-        <v>100000.0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="D10" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" s="10">
         <v>5599.99</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D11" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="7">
-        <v>3630.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="D12" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" s="10">
-        <v>738.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D13" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="7">
         <v>750.01</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="8"/>
+      <c r="B14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="D14" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="10">
-        <v>2078.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>2078.4299999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>11</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D15" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="7">
         <v>2186.16</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>12</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="D16" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="10">
-        <v>640.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>13</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="5"/>
+      <c r="B17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D17" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="7">
-        <v>3575.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>14</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="D18" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="10">
-        <v>2475.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="D19" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="7">
         <v>432.46</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>16</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="8"/>
+      <c r="B20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="D20" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="10">
         <v>1863.39</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>17</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="5"/>
+      <c r="B21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D21" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" s="7">
-        <v>3575.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>18</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="8"/>
+      <c r="B22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="D22" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" s="10">
         <v>1880.81</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>19</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="5"/>
+      <c r="B23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D23" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="7">
-        <v>3630.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>20</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="8"/>
+      <c r="B24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="D24" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>21</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="5"/>
+      <c r="B25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D25" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E25" s="7">
-        <v>500000.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>22</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="8"/>
+      <c r="B26" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D26" s="8" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E26" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>23</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="D27" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27" s="7">
         <v>1863.39</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>24</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="8"/>
+      <c r="B28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="D28" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" s="10">
         <v>8402.91</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>25</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="D29" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" s="7">
-        <v>9990.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>9990</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>26</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="8"/>
+      <c r="B30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="D30" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" s="10">
-        <v>4565.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>4565</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>27</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="5"/>
+      <c r="B31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D31" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" s="7">
-        <v>20000.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>28</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="8"/>
+      <c r="B32" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="D32" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E32" s="10">
         <v>7273.98</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>29</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D33" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E33" s="7">
-        <v>500000.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>30</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="8"/>
+      <c r="B34" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="D34" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" s="10">
-        <v>70000.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>31</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="5"/>
+      <c r="B35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="D35" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" s="7">
-        <v>44826.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>44826</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>32</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="8"/>
+      <c r="B36" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="D36" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" s="10">
         <v>6193.19</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>33</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D37" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E37" s="7">
-        <v>4675.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>34</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="8"/>
+      <c r="B38" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="D38" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" s="10">
-        <v>500000.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>35</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="D39" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E39" s="7">
         <v>5510.17</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>36</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="8"/>
+      <c r="B40" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="D40" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E40" s="10">
         <v>2040.09</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>37</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D41" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E41" s="7">
         <v>563.14</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>38</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="8"/>
+      <c r="B42" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="D42" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E42" s="10">
-        <v>250000.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>39</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="D43" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E43" s="7">
         <v>5555.24</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D44" s="11" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="E44" s="12">
         <f>SUM(E5:E43)</f>
@@ -1047,64 +1372,49 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.7" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1113,7 +1423,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1122,7 +1432,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -1131,7 +1441,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1140,7 +1450,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -1149,7 +1459,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1158,9 +1468,9 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C11" s="11" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="D11" s="12">
         <f>SUM(D5:D10)</f>
@@ -1168,17 +1478,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\BERNARDO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BB97B6-694A-4182-BCF9-52ACEE2E9B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BAC83EFD7C94A1C61E0FF072D0E5C25952EFC69E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
   <si>
     <t>Facturas De Bernardo</t>
   </si>
@@ -81,7 +81,7 @@
     <t>0E4022D0-BCE2-4973-BDDA-1FCA18FB834E</t>
   </si>
   <si>
-    <t>02/06/2026</t>
+    <t>31/05/2026</t>
   </si>
   <si>
     <t>1CD2BDA8-B267-48ED-8F38-3A3F8139E924</t>
@@ -193,9 +193,6 @@
   </si>
   <si>
     <t>CFC606C3-15C7-4C12-A1E6-C07B424B8E52</t>
-  </si>
-  <si>
-    <t>31/05/2026</t>
   </si>
   <si>
     <t>D2D97534-FD69-4212-96CE-6725D6EA60C0</t>
@@ -1217,7 +1214,7 @@
         <v>52</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>9</v>
@@ -1231,7 +1228,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>20</v>
@@ -1248,7 +1245,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>20</v>
@@ -1265,10 +1262,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>9</v>
@@ -1282,7 +1279,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>11</v>
@@ -1299,7 +1296,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>8</v>
@@ -1316,7 +1313,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>20</v>
@@ -1333,7 +1330,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>15</v>
@@ -1350,7 +1347,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>11</v>
@@ -1364,7 +1361,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D44" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E44" s="12">
         <f>SUM(E5:E43)</f>
@@ -1389,7 +1386,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1402,13 +1399,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>3</v>
@@ -1470,7 +1467,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C11" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="12">
         <f>SUM(D5:D10)</f>

--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
@@ -1,40 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\BERNARDO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BAC83EFD7C94A1C61E0FF072D0E5C25952EFC69E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Facturas" sheetId="1" r:id="rId1"/>
-    <sheet name="Fichas" sheetId="2" r:id="rId2"/>
+    <sheet name="Facturas" sheetId="1" r:id="rId4"/>
+    <sheet name="Fichas" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
   <si>
     <t>Facturas De Bernardo</t>
   </si>
@@ -235,41 +217,60 @@
   </si>
   <si>
     <t>MONTO</t>
+  </si>
+  <si>
+    <t>gamaliel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="16"/>
       <color rgb="FF548235"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -334,41 +335,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -658,28 +651,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="43.561" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="29.279" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.425" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -696,7 +692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -713,7 +709,7 @@
         <v>12126.34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -730,7 +726,7 @@
         <v>572.64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -744,10 +740,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -761,10 +757,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="10">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -778,10 +774,10 @@
         <v>9</v>
       </c>
       <c r="E9" s="7">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -798,7 +794,7 @@
         <v>5599.99</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -812,10 +808,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="7">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3630.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -829,10 +825,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="10">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>738.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -849,7 +845,7 @@
         <v>750.01</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -863,10 +859,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="10">
-        <v>2078.4299999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2078.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -883,7 +879,7 @@
         <v>2186.16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -897,10 +893,10 @@
         <v>9</v>
       </c>
       <c r="E16" s="10">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>640.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -914,10 +910,10 @@
         <v>9</v>
       </c>
       <c r="E17" s="7">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3575.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -931,10 +927,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="10">
-        <v>2475</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2475.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="5">
         <v>15</v>
       </c>
@@ -951,7 +947,7 @@
         <v>432.46</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -968,7 +964,7 @@
         <v>1863.39</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="5">
         <v>17</v>
       </c>
@@ -982,10 +978,10 @@
         <v>9</v>
       </c>
       <c r="E21" s="7">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3575.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -1002,7 +998,7 @@
         <v>1880.81</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="5">
         <v>19</v>
       </c>
@@ -1016,10 +1012,10 @@
         <v>9</v>
       </c>
       <c r="E23" s="7">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3630.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -1033,10 +1029,10 @@
         <v>9</v>
       </c>
       <c r="E24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="5">
         <v>21</v>
       </c>
@@ -1050,10 +1046,10 @@
         <v>9</v>
       </c>
       <c r="E25" s="7">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -1067,10 +1063,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="5">
         <v>23</v>
       </c>
@@ -1087,7 +1083,7 @@
         <v>1863.39</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -1104,7 +1100,7 @@
         <v>8402.91</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="5">
         <v>25</v>
       </c>
@@ -1118,10 +1114,10 @@
         <v>9</v>
       </c>
       <c r="E29" s="7">
-        <v>9990</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9990.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -1135,10 +1131,10 @@
         <v>9</v>
       </c>
       <c r="E30" s="10">
-        <v>4565</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4565.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="5">
         <v>27</v>
       </c>
@@ -1152,10 +1148,10 @@
         <v>9</v>
       </c>
       <c r="E31" s="7">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20000.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -1172,7 +1168,7 @@
         <v>7273.98</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="5">
         <v>29</v>
       </c>
@@ -1186,10 +1182,10 @@
         <v>9</v>
       </c>
       <c r="E33" s="7">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -1203,10 +1199,10 @@
         <v>9</v>
       </c>
       <c r="E34" s="10">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="5">
         <v>31</v>
       </c>
@@ -1220,10 +1216,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="7">
-        <v>44826</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>44826.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="8">
         <v>32</v>
       </c>
@@ -1240,7 +1236,7 @@
         <v>6193.19</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="5">
         <v>33</v>
       </c>
@@ -1254,10 +1250,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="7">
-        <v>4675</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4675.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -1271,10 +1267,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="10">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="5">
         <v>35</v>
       </c>
@@ -1291,7 +1287,7 @@
         <v>5510.17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -1308,7 +1304,7 @@
         <v>2040.09</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="5">
         <v>37</v>
       </c>
@@ -1325,7 +1321,7 @@
         <v>563.14</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="8">
         <v>38</v>
       </c>
@@ -1339,10 +1335,10 @@
         <v>9</v>
       </c>
       <c r="E42" s="10">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>250000.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="5">
         <v>39</v>
       </c>
@@ -1359,7 +1355,7 @@
         <v>5555.24</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="D44" s="11" t="s">
         <v>62</v>
       </c>
@@ -1369,32 +1365,62 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1411,16 +1437,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1429,7 +1457,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -1438,7 +1466,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1447,7 +1475,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -1456,7 +1484,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1465,7 +1493,9 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
+      <c r="A11"/>
+      <c r="B11"/>
       <c r="C11" s="11" t="s">
         <v>62</v>
       </c>
@@ -1473,8 +1503,20 @@
         <f>SUM(D5:D10)</f>
         <v>0</v>
       </c>
+      <c r="E11"/>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
@@ -1,22 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\BERNARDO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742AEF53-8F39-4554-A1AD-EA7A790B8A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Facturas" sheetId="1" r:id="rId4"/>
-    <sheet name="Fichas" sheetId="2" r:id="rId5"/>
+    <sheet name="Facturas" sheetId="1" r:id="rId1"/>
+    <sheet name="Fichas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
   <si>
     <t>Facturas De Bernardo</t>
   </si>
@@ -217,60 +235,41 @@
   </si>
   <si>
     <t>MONTO</t>
-  </si>
-  <si>
-    <t>gamaliel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF548235"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -335,33 +334,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -651,31 +658,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="43.561" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -692,7 +696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -709,7 +713,7 @@
         <v>12126.34</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -726,7 +730,7 @@
         <v>572.64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -740,10 +744,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -757,10 +761,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="10">
-        <v>200000.0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -774,10 +778,10 @@
         <v>9</v>
       </c>
       <c r="E9" s="7">
-        <v>100000.0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -794,7 +798,7 @@
         <v>5599.99</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -808,10 +812,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="7">
-        <v>3630.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -825,10 +829,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="10">
-        <v>738.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -845,7 +849,7 @@
         <v>750.01</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -859,10 +863,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="10">
-        <v>2078.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>2078.4299999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -879,7 +883,7 @@
         <v>2186.16</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -893,10 +897,10 @@
         <v>9</v>
       </c>
       <c r="E16" s="10">
-        <v>640.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -910,10 +914,10 @@
         <v>9</v>
       </c>
       <c r="E17" s="7">
-        <v>3575.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -927,10 +931,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="10">
-        <v>2475.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>15</v>
       </c>
@@ -947,7 +951,7 @@
         <v>432.46</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -964,7 +968,7 @@
         <v>1863.39</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>17</v>
       </c>
@@ -978,10 +982,10 @@
         <v>9</v>
       </c>
       <c r="E21" s="7">
-        <v>3575.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -998,7 +1002,7 @@
         <v>1880.81</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>19</v>
       </c>
@@ -1012,10 +1016,10 @@
         <v>9</v>
       </c>
       <c r="E23" s="7">
-        <v>3630.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -1029,10 +1033,10 @@
         <v>9</v>
       </c>
       <c r="E24" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>21</v>
       </c>
@@ -1046,10 +1050,10 @@
         <v>9</v>
       </c>
       <c r="E25" s="7">
-        <v>500000.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -1063,10 +1067,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>23</v>
       </c>
@@ -1083,7 +1087,7 @@
         <v>1863.39</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -1100,7 +1104,7 @@
         <v>8402.91</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>25</v>
       </c>
@@ -1114,10 +1118,10 @@
         <v>9</v>
       </c>
       <c r="E29" s="7">
-        <v>9990.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>9990</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -1131,10 +1135,10 @@
         <v>9</v>
       </c>
       <c r="E30" s="10">
-        <v>4565.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>4565</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>27</v>
       </c>
@@ -1148,10 +1152,10 @@
         <v>9</v>
       </c>
       <c r="E31" s="7">
-        <v>20000.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -1168,7 +1172,7 @@
         <v>7273.98</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>29</v>
       </c>
@@ -1182,10 +1186,10 @@
         <v>9</v>
       </c>
       <c r="E33" s="7">
-        <v>500000.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -1199,10 +1203,10 @@
         <v>9</v>
       </c>
       <c r="E34" s="10">
-        <v>70000.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>31</v>
       </c>
@@ -1216,10 +1220,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="7">
-        <v>44826.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>44826</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>32</v>
       </c>
@@ -1236,7 +1240,7 @@
         <v>6193.19</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>33</v>
       </c>
@@ -1250,10 +1254,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="7">
-        <v>4675.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -1267,10 +1271,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="10">
-        <v>500000.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>35</v>
       </c>
@@ -1287,7 +1291,7 @@
         <v>5510.17</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -1304,7 +1308,7 @@
         <v>2040.09</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>37</v>
       </c>
@@ -1321,7 +1325,7 @@
         <v>563.14</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>38</v>
       </c>
@@ -1335,10 +1339,10 @@
         <v>9</v>
       </c>
       <c r="E42" s="10">
-        <v>250000.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>39</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>5555.24</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D44" s="11" t="s">
         <v>62</v>
       </c>
@@ -1365,62 +1369,32 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>63</v>
       </c>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1437,18 +1411,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>67</v>
-      </c>
+      <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="7"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1457,7 +1429,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -1466,7 +1438,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1475,7 +1447,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -1484,7 +1456,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1493,9 +1465,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11"/>
-      <c r="B11"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C11" s="11" t="s">
         <v>62</v>
       </c>
@@ -1503,20 +1473,8 @@
         <f>SUM(D5:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_MAYO-2026.xlsx
@@ -1,40 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\BERNARDO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742AEF53-8F39-4554-A1AD-EA7A790B8A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Facturas" sheetId="1" r:id="rId1"/>
-    <sheet name="Fichas" sheetId="2" r:id="rId2"/>
+    <sheet name="Facturas" sheetId="1" r:id="rId4"/>
+    <sheet name="Fichas" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
   <si>
     <t>Facturas De Bernardo</t>
   </si>
@@ -235,41 +217,60 @@
   </si>
   <si>
     <t>MONTO</t>
+  </si>
+  <si>
+    <t>prueba2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="16"/>
       <color rgb="FF548235"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -334,41 +335,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -658,28 +651,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="43.561" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="29.279" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.425" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -696,7 +692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -713,7 +709,7 @@
         <v>12126.34</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -730,7 +726,7 @@
         <v>572.64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -744,10 +740,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -761,10 +757,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="10">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -778,10 +774,10 @@
         <v>9</v>
       </c>
       <c r="E9" s="7">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -798,7 +794,7 @@
         <v>5599.99</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -812,10 +808,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="7">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3630.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -829,10 +825,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="10">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>738.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -849,7 +845,7 @@
         <v>750.01</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -863,10 +859,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="10">
-        <v>2078.4299999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2078.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -883,7 +879,7 @@
         <v>2186.16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -897,10 +893,10 @@
         <v>9</v>
       </c>
       <c r="E16" s="10">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>640.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -914,10 +910,10 @@
         <v>9</v>
       </c>
       <c r="E17" s="7">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3575.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -931,10 +927,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="10">
-        <v>2475</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2475.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="5">
         <v>15</v>
       </c>
@@ -951,7 +947,7 @@
         <v>432.46</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -968,7 +964,7 @@
         <v>1863.39</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="5">
         <v>17</v>
       </c>
@@ -982,10 +978,10 @@
         <v>9</v>
       </c>
       <c r="E21" s="7">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3575.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -1002,7 +998,7 @@
         <v>1880.81</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="5">
         <v>19</v>
       </c>
@@ -1016,10 +1012,10 @@
         <v>9</v>
       </c>
       <c r="E23" s="7">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3630.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -1033,10 +1029,10 @@
         <v>9</v>
       </c>
       <c r="E24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="5">
         <v>21</v>
       </c>
@@ -1050,10 +1046,10 @@
         <v>9</v>
       </c>
       <c r="E25" s="7">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -1067,10 +1063,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="5">
         <v>23</v>
       </c>
@@ -1087,7 +1083,7 @@
         <v>1863.39</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -1104,7 +1100,7 @@
         <v>8402.91</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="5">
         <v>25</v>
       </c>
@@ -1118,10 +1114,10 @@
         <v>9</v>
       </c>
       <c r="E29" s="7">
-        <v>9990</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9990.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -1135,10 +1131,10 @@
         <v>9</v>
       </c>
       <c r="E30" s="10">
-        <v>4565</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4565.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="5">
         <v>27</v>
       </c>
@@ -1152,10 +1148,10 @@
         <v>9</v>
       </c>
       <c r="E31" s="7">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20000.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -1172,7 +1168,7 @@
         <v>7273.98</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="5">
         <v>29</v>
       </c>
@@ -1186,10 +1182,10 @@
         <v>9</v>
       </c>
       <c r="E33" s="7">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -1203,10 +1199,10 @@
         <v>9</v>
       </c>
       <c r="E34" s="10">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="5">
         <v>31</v>
       </c>
@@ -1220,10 +1216,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="7">
-        <v>44826</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>44826.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="8">
         <v>32</v>
       </c>
@@ -1240,7 +1236,7 @@
         <v>6193.19</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="5">
         <v>33</v>
       </c>
@@ -1254,10 +1250,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="7">
-        <v>4675</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4675.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -1271,10 +1267,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="10">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="5">
         <v>35</v>
       </c>
@@ -1291,7 +1287,7 @@
         <v>5510.17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -1308,7 +1304,7 @@
         <v>2040.09</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="5">
         <v>37</v>
       </c>
@@ -1325,7 +1321,7 @@
         <v>563.14</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="8">
         <v>38</v>
       </c>
@@ -1339,10 +1335,10 @@
         <v>9</v>
       </c>
       <c r="E42" s="10">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>250000.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="5">
         <v>39</v>
       </c>
@@ -1359,7 +1355,7 @@
         <v>5555.24</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="D44" s="11" t="s">
         <v>62</v>
       </c>
@@ -1369,32 +1365,62 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.703" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1411,16 +1437,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1429,7 +1457,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -1438,7 +1466,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1447,7 +1475,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -1456,7 +1484,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1465,7 +1493,9 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
+      <c r="A11"/>
+      <c r="B11"/>
       <c r="C11" s="11" t="s">
         <v>62</v>
       </c>
@@ -1473,8 +1503,20 @@
         <f>SUM(D5:D10)</f>
         <v>0</v>
       </c>
+      <c r="E11"/>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>